--- a/data/trans_camb/P16A10-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A10-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 4,12</t>
+          <t>-1,76; 4,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 4,08</t>
+          <t>-2,0; 4,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 2,5</t>
+          <t>-2,76; 2,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,61; -1,17</t>
+          <t>-6,38; -1,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 4,29</t>
+          <t>-2,72; 4,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 0,63</t>
+          <t>-4,55; 0,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 1,26</t>
+          <t>-3,01; 1,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 3,34</t>
+          <t>-1,23; 3,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,8</t>
+          <t>-2,7; 1,09</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-34,43; 116,86</t>
+          <t>-33,73; 128,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-33,41; 121,39</t>
+          <t>-33,36; 124,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-44,56; 80,68</t>
+          <t>-44,26; 81,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -18,18</t>
+          <t>-100,0; -12,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-46,61; 186,72</t>
+          <t>-49,64; 175,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-70,57; 35,27</t>
+          <t>-71,38; 33,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-53,75; 39,41</t>
+          <t>-53,33; 36,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,4; 95,26</t>
+          <t>-24,52; 99,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-46,93; 27,98</t>
+          <t>-47,43; 35,41</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 3,23</t>
+          <t>-2,37; 3,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 3,94</t>
+          <t>-1,54; 4,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 3,68</t>
+          <t>-1,37; 3,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 0,93</t>
+          <t>-2,86; 0,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 2,35</t>
+          <t>-2,05; 2,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 1,63</t>
+          <t>-2,46; 1,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,52</t>
+          <t>-1,96; 1,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,5</t>
+          <t>-1,07; 2,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,31</t>
+          <t>-0,9; 2,46</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-52,65; 156,14</t>
+          <t>-51,99; 161,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-33,84; 185,51</t>
+          <t>-35,99; 223,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,7; 173,69</t>
+          <t>-27,02; 192,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 244,19</t>
+          <t>-100,0; 239,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-79,87; 320,92</t>
+          <t>-83,56; 404,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,58; 269,52</t>
+          <t>-70,45; 232,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-58,56; 95,19</t>
+          <t>-56,45; 109,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,91; 132,97</t>
+          <t>-34,04; 144,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-23,66; 136,17</t>
+          <t>-24,81; 139,84</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 2,45</t>
+          <t>-2,97; 2,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 3,67</t>
+          <t>-1,83; 3,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 2,19</t>
+          <t>-6,67; 2,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 3,85</t>
+          <t>-3,32; 3,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 6,94</t>
+          <t>-2,42; 6,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 8,14</t>
+          <t>-0,96; 8,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 2,03</t>
+          <t>-2,45; 2,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 3,6</t>
+          <t>-1,32; 3,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 2,43</t>
+          <t>-4,49; 2,49</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,03; 50,1</t>
+          <t>-39,32; 56,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,79; 79,04</t>
+          <t>-25,33; 82,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-76,52; 38,04</t>
+          <t>-79,07; 38,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-68,02; 243,05</t>
+          <t>-63,69; 248,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-59,49; 401,44</t>
+          <t>-54,64; 436,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,62; 504,04</t>
+          <t>-26,19; 532,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,36; 51,83</t>
+          <t>-36,22; 49,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,28; 83,57</t>
+          <t>-20,87; 81,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-67,57; 46,79</t>
+          <t>-66,47; 51,4</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,48</t>
+          <t>-3,27; 0,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,74</t>
+          <t>-2,1; 2,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 1,89</t>
+          <t>-2,27; 1,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 0,62</t>
+          <t>-3,27; 0,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 1,39</t>
+          <t>-2,62; 1,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 0,54</t>
+          <t>-3,55; 0,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 0,08</t>
+          <t>-2,74; 0,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,9</t>
+          <t>-1,9; 1,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 0,59</t>
+          <t>-2,99; 0,39</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,23; 7,44</t>
+          <t>-40,15; 13,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-28,96; 28,65</t>
+          <t>-25,54; 31,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,25; 29,57</t>
+          <t>-27,55; 29,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-60,83; 21,92</t>
+          <t>-60,99; 21,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-48,69; 45,36</t>
+          <t>-48,39; 44,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,8; 16,16</t>
+          <t>-68,66; 15,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-42,37; 2,6</t>
+          <t>-40,32; 2,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,29; 18,2</t>
+          <t>-28,67; 19,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-43,61; 10,82</t>
+          <t>-44,84; 7,77</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 3,65</t>
+          <t>-2,31; 3,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 4,43</t>
+          <t>-1,64; 4,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 3,5</t>
+          <t>-2,54; 3,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 4,8</t>
+          <t>-0,91; 4,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 2,51</t>
+          <t>-3,29; 2,01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,81</t>
+          <t>-2,46; 2,8</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,35</t>
+          <t>-0,69; 3,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 2,27</t>
+          <t>-1,8; 2,3</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 2,46</t>
+          <t>-1,8; 2,17</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-39,01; 107,28</t>
+          <t>-34,74; 112,95</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-22,97; 113,64</t>
+          <t>-22,27; 131,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-34,21; 93,01</t>
+          <t>-34,19; 92,59</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,76; 98,15</t>
+          <t>-12,32; 100,91</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-42,87; 52,08</t>
+          <t>-42,42; 43,14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-31,35; 56,91</t>
+          <t>-30,41; 59,72</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 73,2</t>
+          <t>-10,16; 70,09</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-25,17; 47,14</t>
+          <t>-24,73; 49,47</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 53,09</t>
+          <t>-24,45; 42,79</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,1; 4,72</t>
+          <t>0,16; 4,81</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,0</t>
+          <t>-1,38; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,95</t>
+          <t>-0,63; 0,91</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,26</t>
+          <t>-2,83; 1,34</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 3,16</t>
+          <t>-1,42; 3,24</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,63</t>
+          <t>-0,67; 3,63</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,46</t>
+          <t>-1,95; 1,42</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,72</t>
+          <t>-1,26; 2,42</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,63</t>
+          <t>-0,74; 2,58</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-32,52; 21,87</t>
+          <t>-34,22; 19,86</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 51,51</t>
+          <t>-18,18; 51,42</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 59,45</t>
+          <t>-7,77; 60,83</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-30,69; 29,2</t>
+          <t>-29,69; 28,92</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 54,26</t>
+          <t>-17,88; 47,59</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 53,71</t>
+          <t>-11,73; 53,65</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,9</t>
+          <t>-1,16; 1,02</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 1,74</t>
+          <t>-0,46; 1,85</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,99</t>
+          <t>-1,39; 1,01</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,58</t>
+          <t>-1,67; 0,54</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,25</t>
+          <t>-1,1; 1,23</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,73</t>
+          <t>-1,5; 0,72</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,4</t>
+          <t>-1,13; 0,37</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,14</t>
+          <t>-0,42; 1,14</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 0,54</t>
+          <t>-1,12; 0,67</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-20,74; 18,06</t>
+          <t>-19,25; 20,86</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 35,28</t>
+          <t>-7,67; 38,65</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-25,36; 19,99</t>
+          <t>-23,17; 20,71</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-27,41; 12,08</t>
+          <t>-29,16; 11,5</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 25,79</t>
+          <t>-18,75; 25,77</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 15,46</t>
+          <t>-25,74; 14,49</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-19,51; 8,14</t>
+          <t>-19,72; 7,34</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 22,79</t>
+          <t>-7,26; 22,88</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 10,86</t>
+          <t>-19,19; 13,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A10-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A10-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,61</t>
+          <t>-1,47</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,79</t>
+          <t>-0,47</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 4,2</t>
+          <t>-2,12; 3,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 4,18</t>
+          <t>-1,88; 3,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 2,42</t>
+          <t>-2,11; 2,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,38; -1,19</t>
+          <t>-6,32; -1,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 4,18</t>
+          <t>-2,69; 4,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 0,66</t>
+          <t>-4,66; 0,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,18</t>
+          <t>-3,07; 1,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 3,3</t>
+          <t>-1,36; 3,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 1,09</t>
+          <t>-2,61; 1,23</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-39,64%</t>
+          <t>-36,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-17,81%</t>
+          <t>-10,6%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,73; 128,02</t>
+          <t>-34,9; 109,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-33,36; 124,12</t>
+          <t>-34,96; 124,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-44,26; 81,18</t>
+          <t>-35,77; 87,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -12,04</t>
+          <t>-100,0; -11,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,64; 175,71</t>
+          <t>-49,81; 170,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-71,38; 33,44</t>
+          <t>-69,65; 40,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-53,33; 36,75</t>
+          <t>-55,67; 33,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 99,81</t>
+          <t>-26,6; 87,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-47,43; 35,41</t>
+          <t>-43,84; 40,91</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>0,73</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 3,25</t>
+          <t>-2,63; 3,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 4,33</t>
+          <t>-1,64; 4,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 3,76</t>
+          <t>-1,53; 3,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 0,86</t>
+          <t>-3,06; 0,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 2,47</t>
+          <t>-2,25; 2,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 1,51</t>
+          <t>-2,38; 1,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,69</t>
+          <t>-1,98; 1,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,53</t>
+          <t>-1,16; 2,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,46</t>
+          <t>-0,96; 2,34</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-2,83%</t>
+          <t>-7,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,99; 161,29</t>
+          <t>-56,18; 146,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-35,99; 223,18</t>
+          <t>-35,53; 188,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,02; 192,46</t>
+          <t>-30,08; 178,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 239,38</t>
+          <t>-100,0; 219,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-83,56; 404,19</t>
+          <t>-83,39; 341,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,45; 232,9</t>
+          <t>-71,64; 192,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-56,45; 109,39</t>
+          <t>-56,94; 87,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,04; 144,6</t>
+          <t>-37,01; 143,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-24,81; 139,84</t>
+          <t>-27,83; 135,98</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,55</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,25</t>
+          <t>3,41</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>1,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 2,59</t>
+          <t>-2,95; 2,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,99</t>
+          <t>-2,21; 3,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 2,2</t>
+          <t>-1,82; 3,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 3,74</t>
+          <t>-3,51; 3,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 6,72</t>
+          <t>-2,65; 6,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 8,0</t>
+          <t>-0,8; 9,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 2,12</t>
+          <t>-2,71; 2,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 3,55</t>
+          <t>-1,44; 3,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 2,49</t>
+          <t>-0,98; 4,06</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-25,18%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-8,95%</t>
+          <t>28,52%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-39,32; 56,17</t>
+          <t>-37,64; 57,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,33; 82,22</t>
+          <t>-29,2; 83,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-79,07; 38,34</t>
+          <t>-26,04; 79,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-63,69; 248,74</t>
+          <t>-64,29; 255,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-54,64; 436,17</t>
+          <t>-52,85; 477,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,19; 532,05</t>
+          <t>-26,05; 563,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-36,22; 49,29</t>
+          <t>-39,31; 46,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,87; 81,92</t>
+          <t>-23,59; 75,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-66,47; 51,4</t>
+          <t>-15,79; 93,45</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,11</t>
+          <t>-0,27</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,17</t>
+          <t>-0,5</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,0</t>
+          <t>-0,58</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 0,76</t>
+          <t>-3,38; 0,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 2,09</t>
+          <t>-2,42; 1,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,92</t>
+          <t>-2,23; 1,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 0,61</t>
+          <t>-3,3; 0,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 1,34</t>
+          <t>-2,41; 1,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,55</t>
+          <t>-2,32; 1,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,11</t>
+          <t>-2,86; -0,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,02</t>
+          <t>-1,87; 1,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 0,39</t>
+          <t>-1,92; 0,91</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-1,49%</t>
+          <t>-3,78%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-28,82%</t>
+          <t>-12,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-16,53%</t>
+          <t>-9,52%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,15; 13,05</t>
+          <t>-42,28; 9,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-25,54; 31,83</t>
+          <t>-29,11; 28,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-27,55; 29,92</t>
+          <t>-26,96; 23,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-60,99; 21,9</t>
+          <t>-62,7; 23,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-48,39; 44,99</t>
+          <t>-45,22; 58,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,66; 15,47</t>
+          <t>-44,09; 49,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-40,32; 2,84</t>
+          <t>-42,35; -0,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,67; 19,24</t>
+          <t>-27,86; 20,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-44,84; 7,77</t>
+          <t>-28,11; 17,03</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>0,7</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 3,82</t>
+          <t>-2,67; 3,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 4,49</t>
+          <t>-1,49; 4,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 3,31</t>
+          <t>-2,84; 2,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 4,86</t>
+          <t>-1,08; 4,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 2,01</t>
+          <t>-3,4; 1,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 2,8</t>
+          <t>-1,22; 3,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,46</t>
+          <t>-0,93; 3,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 2,3</t>
+          <t>-1,87; 2,4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 2,17</t>
+          <t>-1,27; 2,34</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-34,74; 112,95</t>
+          <t>-35,78; 87,99</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-22,27; 131,84</t>
+          <t>-21,08; 134,2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-34,19; 92,59</t>
+          <t>-40,91; 72,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 100,91</t>
+          <t>-13,98; 97,01</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-42,42; 43,14</t>
+          <t>-42,78; 45,24</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-30,41; 59,72</t>
+          <t>-16,09; 75,02</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 70,09</t>
+          <t>-13,13; 71,42</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-24,73; 49,47</t>
+          <t>-25,73; 50,86</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-24,45; 42,79</t>
+          <t>-17,43; 51,06</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,15</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>1,47</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>1,0</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,16; 4,81</t>
+          <t>0,11; 4,89</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,0</t>
+          <t>-1,46; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,91</t>
+          <t>-0,62; 0,92</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 1,34</t>
+          <t>-2,91; 1,22</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 3,24</t>
+          <t>-1,34; 3,33</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,63</t>
+          <t>-0,82; 3,44</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,42</t>
+          <t>-2,08; 1,43</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,42</t>
+          <t>-1,12; 2,48</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,58</t>
+          <t>-0,62; 2,79</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>17,28%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-34,22; 19,86</t>
+          <t>-35,98; 20,03</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 51,42</t>
+          <t>-16,8; 55,09</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 60,83</t>
+          <t>-9,96; 58,04</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-29,69; 28,92</t>
+          <t>-30,93; 30,44</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-17,88; 47,59</t>
+          <t>-17,98; 52,57</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 53,65</t>
+          <t>-9,7; 58,74</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-0,2</t>
+          <t>0,21</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,02</t>
+          <t>-1,18; 1,06</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,85</t>
+          <t>-0,59; 1,64</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 1,01</t>
+          <t>-0,86; 1,2</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,54</t>
+          <t>-1,66; 0,44</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 1,23</t>
+          <t>-1,08; 1,3</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,72</t>
+          <t>-0,8; 1,18</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,37</t>
+          <t>-1,09; 0,43</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,14</t>
+          <t>-0,56; 1,09</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,67</t>
+          <t>-0,48; 0,94</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-1,77%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-5,43%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-3,64%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-19,25; 20,86</t>
+          <t>-20,22; 20,96</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 38,65</t>
+          <t>-9,98; 33,87</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-23,17; 20,71</t>
+          <t>-14,26; 24,78</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-29,16; 11,5</t>
+          <t>-27,7; 9,39</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 25,77</t>
+          <t>-18,05; 26,95</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 14,49</t>
+          <t>-13,77; 24,55</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-19,72; 7,34</t>
+          <t>-18,74; 8,95</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 22,88</t>
+          <t>-9,5; 22,05</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 13,46</t>
+          <t>-8,49; 19,36</t>
         </is>
       </c>
     </row>
